--- a/mosip_master/xlsx/loc_hierarchy_list.xlsx
+++ b/mosip_master/xlsx/loc_hierarchy_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50E26FE-30F0-4867-B349-C0B819484B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F090238-B8B7-4DF9-8188-0580C162711C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3220" yWindow="4740" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
   <si>
     <t>lang_code</t>
   </si>
@@ -54,10 +54,16 @@
     <t>City</t>
   </si>
   <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Postal code</t>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
   </si>
 </sst>
 </file>
@@ -499,7 +505,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
@@ -513,9 +519,37 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
